--- a/data/tasques/02.20/ADG32/entregues/5796/02.20-5796-06_FACTURES_VENDA.xlsx
+++ b/data/tasques/02.20/ADG32/entregues/5796/02.20-5796-06_FACTURES_VENDA.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="152">
   <si>
     <t>Número</t>
   </si>
@@ -46,64 +46,265 @@
     <t>Enviado</t>
   </si>
   <si>
-    <t>FV-1/2026/00010</t>
+    <t>FV-1/2026/00009</t>
+  </si>
+  <si>
+    <t>BIGCORP SL</t>
+  </si>
+  <si>
+    <t>C-V/00073</t>
+  </si>
+  <si>
+    <t>Pagada</t>
+  </si>
+  <si>
+    <t>No enviado</t>
+  </si>
+  <si>
+    <t>FV-1/2026/00008</t>
   </si>
   <si>
     <t>COMERCIAL CALCO SA</t>
   </si>
   <si>
-    <t>C-V/00075, C-V/00074, C-V/00076</t>
-  </si>
-  <si>
-    <t>Pagada</t>
-  </si>
-  <si>
-    <t>No enviado</t>
-  </si>
-  <si>
-    <t>FV-1/2026/00009</t>
-  </si>
-  <si>
-    <t>BIGCORP SL</t>
+    <t>C-V/00075, C-V/00074</t>
+  </si>
+  <si>
+    <t>FV-2/2026/00024</t>
+  </si>
+  <si>
+    <t>ADG32 6844 TTRAMULLAS SL</t>
+  </si>
+  <si>
+    <t>C-V/00072</t>
+  </si>
+  <si>
+    <t>FV-2/2026/00023</t>
+  </si>
+  <si>
+    <t>ADG32 6792 PCAPO SL</t>
+  </si>
+  <si>
+    <t>C-V/00071</t>
+  </si>
+  <si>
+    <t>FV-2/2026/00022</t>
+  </si>
+  <si>
+    <t>ADG32 6428 ABOUBAL SL</t>
+  </si>
+  <si>
+    <t>C-V/00070</t>
+  </si>
+  <si>
+    <t>FV-2/2026/00021</t>
+  </si>
+  <si>
+    <t>ADG32 6707 MOUAZINE SL</t>
+  </si>
+  <si>
+    <t>C-V/00066</t>
+  </si>
+  <si>
+    <t>FV-2/2026/00020</t>
+  </si>
+  <si>
+    <t>ADG32 6431 GZOUGGAGHI SL</t>
+  </si>
+  <si>
+    <t>C-V/00065</t>
+  </si>
+  <si>
+    <t>FV-2/2026/00019</t>
+  </si>
+  <si>
+    <t>ADG32 6777 JGARCIA SL</t>
+  </si>
+  <si>
+    <t>C-V/00064</t>
+  </si>
+  <si>
+    <t>FV-2/2026/00018</t>
+  </si>
+  <si>
+    <t>ADG32 6368 LPIZA SL</t>
+  </si>
+  <si>
+    <t>C-V/00063</t>
+  </si>
+  <si>
+    <t>FV-2/2026/00017</t>
+  </si>
+  <si>
+    <t>ADG32 6713 BCARBONELL SL</t>
+  </si>
+  <si>
+    <t>C-V/00062</t>
+  </si>
+  <si>
+    <t>FV-2/2026/00016</t>
+  </si>
+  <si>
+    <t>ADG32 6356 WAANANOU SL</t>
+  </si>
+  <si>
+    <t>C-V/00049</t>
+  </si>
+  <si>
+    <t>FV-2/2026/00015</t>
+  </si>
+  <si>
+    <t>ADG32 6427 NANANOU SL</t>
+  </si>
+  <si>
+    <t>C-V/00061</t>
+  </si>
+  <si>
+    <t>FV-2/2026/00014</t>
+  </si>
+  <si>
+    <t>ADG32 6369 VMASTRANGELO SL</t>
   </si>
   <si>
     <t>C-V/00060</t>
   </si>
   <si>
-    <t>FV-1/2026/00008</t>
-  </si>
-  <si>
-    <t>C-V/00059, C-V/00061</t>
+    <t>FV-2/2026/00013</t>
+  </si>
+  <si>
+    <t>ADG32 6467 WCHANTAH SL</t>
+  </si>
+  <si>
+    <t>C-V/00059</t>
+  </si>
+  <si>
+    <t>FV-2/2026/00012</t>
+  </si>
+  <si>
+    <t>ADG32 6706 NSUIYHI SL</t>
+  </si>
+  <si>
+    <t>C-V/00058</t>
+  </si>
+  <si>
+    <t>FV-2/2026/00011</t>
+  </si>
+  <si>
+    <t>ADG32 6320 MNAVARRO SL</t>
+  </si>
+  <si>
+    <t>C-V/00054</t>
+  </si>
+  <si>
+    <t>FV-2/2026/00010</t>
+  </si>
+  <si>
+    <t>ADG32 6265 SMORENO SL</t>
+  </si>
+  <si>
+    <t>C-V/00053</t>
+  </si>
+  <si>
+    <t>FV-2/2026/00009</t>
+  </si>
+  <si>
+    <t>ADG32 6478 CBAUZA SL</t>
+  </si>
+  <si>
+    <t>C-V/00051</t>
+  </si>
+  <si>
+    <t>FV-2/2026/00008</t>
+  </si>
+  <si>
+    <t>ADG32 6352 SAANANOU SL</t>
+  </si>
+  <si>
+    <t>C-V/00050</t>
+  </si>
+  <si>
+    <t>FV-2/2026/00007</t>
+  </si>
+  <si>
+    <t>ADG32 6366 JMORAGUES SL</t>
+  </si>
+  <si>
+    <t>C-V/00048</t>
+  </si>
+  <si>
+    <t>FV-2/2026/00006</t>
+  </si>
+  <si>
+    <t>ADG32 6734 LABOLAFIO SL</t>
+  </si>
+  <si>
+    <t>C-V/00047</t>
+  </si>
+  <si>
+    <t>FV-2/2026/00005</t>
+  </si>
+  <si>
+    <t>ADG32 6746 ELLADO SL</t>
+  </si>
+  <si>
+    <t>C-V/00046</t>
+  </si>
+  <si>
+    <t>FV-2/2026/00004</t>
+  </si>
+  <si>
+    <t>ADG32 6702 NFORNES SL</t>
+  </si>
+  <si>
+    <t>C-V/00045</t>
   </si>
   <si>
     <t>FV-1/2026/00007</t>
   </si>
   <si>
-    <t>C-V/00046</t>
+    <t>C-V/00055</t>
   </si>
   <si>
     <t>FV-1/2026/00006</t>
   </si>
   <si>
-    <t>C-V/00044, C-V/00045</t>
+    <t>C-V/00057, C-V/00056</t>
+  </si>
+  <si>
+    <t>FV-2/2026/00003</t>
+  </si>
+  <si>
+    <t>C-V/00044</t>
+  </si>
+  <si>
+    <t>FV-2/2026/00002</t>
+  </si>
+  <si>
+    <t>C-V/00043</t>
   </si>
   <si>
     <t>FV-1/2026/00005</t>
   </si>
   <si>
-    <t>C-V/00040, C-V/00042, C-V/00041</t>
+    <t>C-V/00040, C-V/00041, C-V/00042</t>
+  </si>
+  <si>
+    <t>FV-2/2026/00001</t>
+  </si>
+  <si>
+    <t>C-V/00039</t>
   </si>
   <si>
     <t>FV-1/2026/00004</t>
   </si>
   <si>
-    <t>C-V/00038</t>
+    <t>C-V/00036, C-V/00038, C-V/00037</t>
   </si>
   <si>
     <t>FV-1/2026/00003</t>
   </si>
   <si>
-    <t>C-V/00037, C-V/00036</t>
+    <t>C-V/00033</t>
   </si>
   <si>
     <t>FV-1/2026/00002</t>
@@ -115,145 +316,154 @@
     <t>FV-1/2026/00001</t>
   </si>
   <si>
-    <t>C-V/00033</t>
+    <t>C-V/00030, C-V/00032, C-V/00031</t>
+  </si>
+  <si>
+    <t>FV-2/2025/00001</t>
+  </si>
+  <si>
+    <t>ADG53 4751 APONS SL</t>
+  </si>
+  <si>
+    <t>C-V/00026</t>
   </si>
   <si>
     <t>FV-1/2025/00024</t>
   </si>
   <si>
-    <t>C-V/00032, C-V/00030</t>
+    <t>C-V/00028</t>
   </si>
   <si>
     <t>FV-1/2025/00023</t>
   </si>
   <si>
-    <t>C-V/00031</t>
+    <t>C-V/00029, C-V/00027</t>
   </si>
   <si>
     <t>FV-1/2025/00022</t>
   </si>
   <si>
-    <t>C-V/00027, C-V/00025</t>
+    <t>C-V/00023, C-V/00025</t>
   </si>
   <si>
     <t>FV-1/2025/00021</t>
   </si>
   <si>
-    <t>C-V/00026</t>
+    <t>C-V/00024</t>
   </si>
   <si>
     <t>FV-1/2025/00020</t>
   </si>
   <si>
-    <t>C-V/00022, C-V/00024</t>
+    <t>C-V/00021, C-V/00020, C-V/00022</t>
   </si>
   <si>
     <t>FV-1/2025/00019</t>
   </si>
   <si>
-    <t>C-V/00023</t>
+    <t>C-V/00019</t>
   </si>
   <si>
     <t>FV-1/2025/00018</t>
   </si>
   <si>
-    <t>C-V/00020, C-V/00021</t>
+    <t>C-V/00018</t>
   </si>
   <si>
     <t>FV-1/2025/00017</t>
   </si>
   <si>
-    <t>C-V/00019</t>
+    <t>C-V/00017</t>
   </si>
   <si>
     <t>FV-1/2025/00016</t>
   </si>
   <si>
-    <t>C-V/00018</t>
+    <t>C-V/00016</t>
   </si>
   <si>
     <t>FV-1/2025/00015</t>
   </si>
   <si>
-    <t>C-V/00017</t>
+    <t>C-V/00015</t>
   </si>
   <si>
     <t>FV-1/2025/00014</t>
   </si>
   <si>
-    <t>C-V/00016</t>
+    <t>C-V/00014</t>
   </si>
   <si>
     <t>FV-1/2025/00013</t>
   </si>
   <si>
-    <t>C-V/00015</t>
+    <t>C-V/00013</t>
   </si>
   <si>
     <t>FV-1/2025/00012</t>
   </si>
   <si>
-    <t>C-V/00014</t>
+    <t>C-V/00012</t>
   </si>
   <si>
     <t>FV-1/2025/00011</t>
   </si>
   <si>
-    <t>C-V/00013</t>
+    <t>C-V/00011</t>
   </si>
   <si>
     <t>FV-1/2025/00010</t>
   </si>
   <si>
-    <t>C-V/00012</t>
+    <t>C-V/00010</t>
   </si>
   <si>
     <t>FV-1/2025/00009</t>
   </si>
   <si>
-    <t>C-V/00011</t>
+    <t>C-V/00009</t>
   </si>
   <si>
     <t>FV-1/2025/00008</t>
   </si>
   <si>
-    <t>C-V/00010</t>
+    <t>C-V/00008</t>
   </si>
   <si>
     <t>FV-1/2025/00007</t>
   </si>
   <si>
-    <t>C-V/00009</t>
+    <t>C-V/00007</t>
   </si>
   <si>
     <t>FV-1/2025/00006</t>
   </si>
   <si>
-    <t>C-V/00008</t>
+    <t>C-V/00006</t>
   </si>
   <si>
     <t>FV-1/2025/00005</t>
   </si>
   <si>
-    <t>C-V/00007</t>
+    <t>C-V/00005</t>
   </si>
   <si>
     <t>FV-1/2025/00004</t>
   </si>
   <si>
-    <t>C-V/00005</t>
+    <t>C-V/00004</t>
   </si>
   <si>
     <t>FV-1/2025/00003</t>
   </si>
   <si>
-    <t>C-V/00004</t>
+    <t>C-V/00003</t>
   </si>
   <si>
     <t>FV-1/2025/00002</t>
   </si>
   <si>
-    <t>C-V/00003</t>
+    <t>C-V/00002</t>
   </si>
   <si>
     <t>FV-1/2025/00001</t>
@@ -613,7 +823,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J35"/>
+  <dimension ref="A1:J59"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="10" width="30.7109375" customWidth="1"/>
@@ -656,10 +866,10 @@
         <v>10</v>
       </c>
       <c r="B2" s="3">
-        <v>46065</v>
+        <v>46064</v>
       </c>
       <c r="C2" s="3">
-        <v>46072</v>
+        <v>46071</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>11</v>
@@ -668,13 +878,13 @@
         <v>12</v>
       </c>
       <c r="F2" s="4">
-        <v>10231.5</v>
+        <v>3885</v>
       </c>
       <c r="G2" s="4">
-        <v>2148.62</v>
+        <v>815.85</v>
       </c>
       <c r="H2" s="4">
-        <v>12380.12</v>
+        <v>4700.85</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>13</v>
@@ -688,10 +898,10 @@
         <v>15</v>
       </c>
       <c r="B3" s="3">
-        <v>46057</v>
+        <v>46064</v>
       </c>
       <c r="C3" s="3">
-        <v>46064</v>
+        <v>46071</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>16</v>
@@ -700,13 +910,13 @@
         <v>17</v>
       </c>
       <c r="F3" s="4">
-        <v>3373.5</v>
+        <v>7515</v>
       </c>
       <c r="G3" s="4">
-        <v>708.4400000000001</v>
+        <v>1578.15</v>
       </c>
       <c r="H3" s="4">
-        <v>4081.94</v>
+        <v>9093.15</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>13</v>
@@ -720,25 +930,25 @@
         <v>18</v>
       </c>
       <c r="B4" s="3">
-        <v>46057</v>
+        <v>46063</v>
       </c>
       <c r="C4" s="3">
-        <v>46064</v>
+        <v>46063</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F4" s="4">
-        <v>7497</v>
+        <v>396</v>
       </c>
       <c r="G4" s="4">
-        <v>1574.37</v>
+        <v>83.16</v>
       </c>
       <c r="H4" s="4">
-        <v>9071.370000000001</v>
+        <v>479.16</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>13</v>
@@ -749,28 +959,28 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B5" s="3">
-        <v>46050</v>
+        <v>46062</v>
       </c>
       <c r="C5" s="3">
-        <v>46057</v>
+        <v>46062</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F5" s="4">
-        <v>3559.5</v>
+        <v>396</v>
       </c>
       <c r="G5" s="4">
-        <v>747.5</v>
+        <v>83.16</v>
       </c>
       <c r="H5" s="4">
-        <v>4307</v>
+        <v>479.16</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>13</v>
@@ -781,28 +991,28 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B6" s="3">
-        <v>46050</v>
+        <v>46062</v>
       </c>
       <c r="C6" s="3">
-        <v>46057</v>
+        <v>46062</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F6" s="4">
-        <v>5901</v>
+        <v>396</v>
       </c>
       <c r="G6" s="4">
-        <v>1239.21</v>
+        <v>83.16</v>
       </c>
       <c r="H6" s="4">
-        <v>7140.21</v>
+        <v>479.16</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>13</v>
@@ -813,28 +1023,28 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B7" s="3">
-        <v>46043</v>
+        <v>46059</v>
       </c>
       <c r="C7" s="3">
-        <v>46050</v>
+        <v>46059</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F7" s="4">
-        <v>10095</v>
+        <v>396</v>
       </c>
       <c r="G7" s="4">
-        <v>2119.95</v>
+        <v>83.16</v>
       </c>
       <c r="H7" s="4">
-        <v>12214.95</v>
+        <v>479.16</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>13</v>
@@ -845,28 +1055,28 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B8" s="3">
-        <v>46036</v>
+        <v>46059</v>
       </c>
       <c r="C8" s="3">
-        <v>46043</v>
+        <v>46059</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F8" s="4">
-        <v>3661.5</v>
+        <v>396</v>
       </c>
       <c r="G8" s="4">
-        <v>768.92</v>
+        <v>83.16</v>
       </c>
       <c r="H8" s="4">
-        <v>4430.42</v>
+        <v>479.16</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>13</v>
@@ -877,28 +1087,28 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B9" s="3">
-        <v>46036</v>
+        <v>46059</v>
       </c>
       <c r="C9" s="3">
-        <v>46043</v>
+        <v>46059</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F9" s="4">
-        <v>6126</v>
+        <v>396</v>
       </c>
       <c r="G9" s="4">
-        <v>1286.46</v>
+        <v>83.16</v>
       </c>
       <c r="H9" s="4">
-        <v>7412.46</v>
+        <v>479.16</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>13</v>
@@ -909,28 +1119,28 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B10" s="3">
-        <v>46030</v>
+        <v>46059</v>
       </c>
       <c r="C10" s="3">
-        <v>46037</v>
+        <v>46059</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="F10" s="4">
-        <v>6436.5</v>
+        <v>396</v>
       </c>
       <c r="G10" s="4">
-        <v>1351.67</v>
+        <v>83.16</v>
       </c>
       <c r="H10" s="4">
-        <v>7788.17</v>
+        <v>479.16</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>13</v>
@@ -941,28 +1151,28 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="B11" s="3">
-        <v>46030</v>
+        <v>46059</v>
       </c>
       <c r="C11" s="3">
-        <v>46037</v>
+        <v>46059</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="F11" s="4">
-        <v>3549</v>
+        <v>396</v>
       </c>
       <c r="G11" s="4">
-        <v>745.29</v>
+        <v>83.16</v>
       </c>
       <c r="H11" s="4">
-        <v>4294.29</v>
+        <v>479.16</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>13</v>
@@ -973,28 +1183,28 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="B12" s="3">
-        <v>46009</v>
+        <v>46059</v>
       </c>
       <c r="C12" s="3">
-        <v>46016</v>
+        <v>46059</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="F12" s="4">
-        <v>5542.5</v>
+        <v>396</v>
       </c>
       <c r="G12" s="4">
-        <v>1163.93</v>
+        <v>83.16</v>
       </c>
       <c r="H12" s="4">
-        <v>6706.43</v>
+        <v>479.16</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>13</v>
@@ -1005,28 +1215,28 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="B13" s="3">
-        <v>46009</v>
+        <v>46059</v>
       </c>
       <c r="C13" s="3">
-        <v>46016</v>
+        <v>46059</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="F13" s="4">
-        <v>3310.5</v>
+        <v>396</v>
       </c>
       <c r="G13" s="4">
-        <v>695.21</v>
+        <v>83.16</v>
       </c>
       <c r="H13" s="4">
-        <v>4005.71</v>
+        <v>479.16</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>13</v>
@@ -1037,28 +1247,28 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="B14" s="3">
-        <v>46001</v>
+        <v>46059</v>
       </c>
       <c r="C14" s="3">
-        <v>46008</v>
+        <v>46059</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="F14" s="4">
-        <v>6484.5</v>
+        <v>396</v>
       </c>
       <c r="G14" s="4">
-        <v>1361.75</v>
+        <v>83.16</v>
       </c>
       <c r="H14" s="4">
-        <v>7846.25</v>
+        <v>479.16</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>13</v>
@@ -1069,28 +1279,28 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="B15" s="3">
-        <v>46001</v>
+        <v>46059</v>
       </c>
       <c r="C15" s="3">
-        <v>46008</v>
+        <v>46059</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="F15" s="4">
-        <v>3037.5</v>
+        <v>396</v>
       </c>
       <c r="G15" s="4">
-        <v>637.88</v>
+        <v>83.16</v>
       </c>
       <c r="H15" s="4">
-        <v>3675.38</v>
+        <v>479.16</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>13</v>
@@ -1101,28 +1311,28 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="B16" s="3">
-        <v>45994</v>
+        <v>46059</v>
       </c>
       <c r="C16" s="3">
-        <v>46001</v>
+        <v>46059</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="F16" s="4">
-        <v>6724.5</v>
+        <v>396</v>
       </c>
       <c r="G16" s="4">
-        <v>1412.15</v>
+        <v>83.16</v>
       </c>
       <c r="H16" s="4">
-        <v>8136.65</v>
+        <v>479.16</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>13</v>
@@ -1133,28 +1343,28 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="B17" s="3">
-        <v>45994</v>
+        <v>46059</v>
       </c>
       <c r="C17" s="3">
-        <v>46001</v>
+        <v>46059</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>11</v>
+        <v>58</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="F17" s="4">
-        <v>3096</v>
+        <v>396</v>
       </c>
       <c r="G17" s="4">
-        <v>650.16</v>
+        <v>83.16</v>
       </c>
       <c r="H17" s="4">
-        <v>3746.16</v>
+        <v>479.16</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>13</v>
@@ -1165,28 +1375,28 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="B18" s="3">
-        <v>45987</v>
+        <v>46059</v>
       </c>
       <c r="C18" s="3">
-        <v>45994</v>
+        <v>46059</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="F18" s="4">
-        <v>6937.5</v>
+        <v>396</v>
       </c>
       <c r="G18" s="4">
-        <v>1456.88</v>
+        <v>83.16</v>
       </c>
       <c r="H18" s="4">
-        <v>8394.379999999999</v>
+        <v>479.16</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>13</v>
@@ -1197,28 +1407,28 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="B19" s="3">
-        <v>45987</v>
+        <v>46059</v>
       </c>
       <c r="C19" s="3">
-        <v>45994</v>
+        <v>46059</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>11</v>
+        <v>64</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="F19" s="4">
-        <v>3135</v>
+        <v>396</v>
       </c>
       <c r="G19" s="4">
-        <v>658.35</v>
+        <v>83.16</v>
       </c>
       <c r="H19" s="4">
-        <v>3793.35</v>
+        <v>479.16</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>13</v>
@@ -1229,28 +1439,28 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="B20" s="3">
-        <v>45980</v>
+        <v>46059</v>
       </c>
       <c r="C20" s="3">
-        <v>45987</v>
+        <v>46059</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="F20" s="4">
-        <v>2844</v>
+        <v>396</v>
       </c>
       <c r="G20" s="4">
-        <v>597.24</v>
+        <v>83.16</v>
       </c>
       <c r="H20" s="4">
-        <v>3441.24</v>
+        <v>479.16</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>13</v>
@@ -1261,28 +1471,28 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="B21" s="3">
-        <v>45980</v>
+        <v>46059</v>
       </c>
       <c r="C21" s="3">
-        <v>45987</v>
+        <v>46059</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="F21" s="4">
-        <v>3069</v>
+        <v>396</v>
       </c>
       <c r="G21" s="4">
-        <v>644.49</v>
+        <v>83.16</v>
       </c>
       <c r="H21" s="4">
-        <v>3713.49</v>
+        <v>479.16</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>13</v>
@@ -1293,28 +1503,28 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="B22" s="3">
-        <v>45980</v>
+        <v>46059</v>
       </c>
       <c r="C22" s="3">
-        <v>45987</v>
+        <v>46059</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>16</v>
+        <v>73</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="F22" s="4">
-        <v>2862</v>
+        <v>396</v>
       </c>
       <c r="G22" s="4">
-        <v>601.02</v>
+        <v>83.16</v>
       </c>
       <c r="H22" s="4">
-        <v>3463.02</v>
+        <v>479.16</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>13</v>
@@ -1325,28 +1535,28 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="B23" s="3">
-        <v>45973</v>
+        <v>46059</v>
       </c>
       <c r="C23" s="3">
-        <v>45980</v>
+        <v>46059</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>16</v>
+        <v>76</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="F23" s="4">
-        <v>2988</v>
+        <v>396</v>
       </c>
       <c r="G23" s="4">
-        <v>627.48</v>
+        <v>83.16</v>
       </c>
       <c r="H23" s="4">
-        <v>3615.48</v>
+        <v>479.16</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>13</v>
@@ -1357,28 +1567,28 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="B24" s="3">
-        <v>45973</v>
+        <v>46059</v>
       </c>
       <c r="C24" s="3">
-        <v>45980</v>
+        <v>46059</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>11</v>
+        <v>79</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="F24" s="4">
-        <v>3369</v>
+        <v>396</v>
       </c>
       <c r="G24" s="4">
-        <v>707.49</v>
+        <v>83.16</v>
       </c>
       <c r="H24" s="4">
-        <v>4076.49</v>
+        <v>479.16</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>13</v>
@@ -1389,28 +1599,28 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="B25" s="3">
-        <v>45973</v>
+        <v>46057</v>
       </c>
       <c r="C25" s="3">
-        <v>45980</v>
+        <v>46064</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="F25" s="4">
-        <v>3921</v>
+        <v>3822</v>
       </c>
       <c r="G25" s="4">
-        <v>823.41</v>
+        <v>802.62</v>
       </c>
       <c r="H25" s="4">
-        <v>4744.41</v>
+        <v>4624.62</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>13</v>
@@ -1421,28 +1631,28 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>62</v>
+        <v>83</v>
       </c>
       <c r="B26" s="3">
-        <v>45966</v>
+        <v>46057</v>
       </c>
       <c r="C26" s="3">
-        <v>45973</v>
+        <v>46064</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="F26" s="4">
-        <v>3837</v>
+        <v>5694</v>
       </c>
       <c r="G26" s="4">
-        <v>805.77</v>
+        <v>1195.74</v>
       </c>
       <c r="H26" s="4">
-        <v>4642.77</v>
+        <v>6889.74</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>13</v>
@@ -1453,28 +1663,28 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>64</v>
+        <v>85</v>
       </c>
       <c r="B27" s="3">
-        <v>45966</v>
+        <v>46051</v>
       </c>
       <c r="C27" s="3">
-        <v>45973</v>
+        <v>46051</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="F27" s="4">
-        <v>3849</v>
+        <v>396</v>
       </c>
       <c r="G27" s="4">
-        <v>808.29</v>
+        <v>83.16</v>
       </c>
       <c r="H27" s="4">
-        <v>4657.29</v>
+        <v>479.16</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>13</v>
@@ -1485,28 +1695,28 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="B28" s="3">
-        <v>45966</v>
+        <v>46051</v>
       </c>
       <c r="C28" s="3">
-        <v>45973</v>
+        <v>46051</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="F28" s="4">
-        <v>3958.5</v>
+        <v>396</v>
       </c>
       <c r="G28" s="4">
-        <v>831.29</v>
+        <v>83.16</v>
       </c>
       <c r="H28" s="4">
-        <v>4789.79</v>
+        <v>479.16</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>13</v>
@@ -1517,28 +1727,28 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>68</v>
+        <v>89</v>
       </c>
       <c r="B29" s="3">
-        <v>45959</v>
+        <v>46051</v>
       </c>
       <c r="C29" s="3">
-        <v>45966</v>
+        <v>46058</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="F29" s="4">
-        <v>2943</v>
+        <v>9855</v>
       </c>
       <c r="G29" s="4">
-        <v>618.03</v>
+        <v>2069.55</v>
       </c>
       <c r="H29" s="4">
-        <v>3561.03</v>
+        <v>11924.55</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>13</v>
@@ -1549,28 +1759,28 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="B30" s="3">
-        <v>45959</v>
+        <v>46045</v>
       </c>
       <c r="C30" s="3">
-        <v>45966</v>
+        <v>46045</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="F30" s="4">
-        <v>2755.5</v>
+        <v>396</v>
       </c>
       <c r="G30" s="4">
-        <v>578.66</v>
+        <v>83.16</v>
       </c>
       <c r="H30" s="4">
-        <v>3334.16</v>
+        <v>479.16</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>13</v>
@@ -1581,28 +1791,28 @@
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="B31" s="3">
-        <v>45959</v>
+        <v>46043</v>
       </c>
       <c r="C31" s="3">
-        <v>45966</v>
+        <v>46050</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="F31" s="4">
-        <v>3198</v>
+        <v>9858</v>
       </c>
       <c r="G31" s="4">
-        <v>671.58</v>
+        <v>2070.18</v>
       </c>
       <c r="H31" s="4">
-        <v>3869.58</v>
+        <v>11928.18</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>13</v>
@@ -1613,28 +1823,28 @@
     </row>
     <row r="32" spans="1:10">
       <c r="A32" s="2" t="s">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="B32" s="3">
-        <v>45952</v>
+        <v>46036</v>
       </c>
       <c r="C32" s="3">
-        <v>45959</v>
+        <v>46043</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="F32" s="4">
-        <v>3504</v>
+        <v>2808</v>
       </c>
       <c r="G32" s="4">
-        <v>735.84</v>
+        <v>589.6799999999999</v>
       </c>
       <c r="H32" s="4">
-        <v>4239.84</v>
+        <v>3397.68</v>
       </c>
       <c r="I32" s="2" t="s">
         <v>13</v>
@@ -1645,28 +1855,28 @@
     </row>
     <row r="33" spans="1:10">
       <c r="A33" s="2" t="s">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="B33" s="3">
-        <v>45952</v>
+        <v>46036</v>
       </c>
       <c r="C33" s="3">
-        <v>45959</v>
+        <v>46043</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>16</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="F33" s="4">
-        <v>3108</v>
+        <v>6666</v>
       </c>
       <c r="G33" s="4">
-        <v>652.6799999999999</v>
+        <v>1399.86</v>
       </c>
       <c r="H33" s="4">
-        <v>3760.68</v>
+        <v>8065.86</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>13</v>
@@ -1677,28 +1887,28 @@
     </row>
     <row r="34" spans="1:10">
       <c r="A34" s="2" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="B34" s="3">
-        <v>45952</v>
+        <v>46031</v>
       </c>
       <c r="C34" s="3">
-        <v>45959</v>
+        <v>46038</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>16</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="F34" s="4">
-        <v>3291</v>
+        <v>10110</v>
       </c>
       <c r="G34" s="4">
-        <v>691.11</v>
+        <v>2123.1</v>
       </c>
       <c r="H34" s="4">
-        <v>3982.11</v>
+        <v>12233.1</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>13</v>
@@ -1709,33 +1919,801 @@
     </row>
     <row r="35" spans="1:10">
       <c r="A35" s="2" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="B35" s="3">
+        <v>46020</v>
+      </c>
+      <c r="C35" s="3">
+        <v>46020</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F35" s="4">
+        <v>396</v>
+      </c>
+      <c r="G35" s="4">
+        <v>83.16</v>
+      </c>
+      <c r="H35" s="4">
+        <v>479.16</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="A36" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B36" s="3">
+        <v>46009</v>
+      </c>
+      <c r="C36" s="3">
+        <v>46016</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F36" s="4">
+        <v>3186</v>
+      </c>
+      <c r="G36" s="4">
+        <v>669.0599999999999</v>
+      </c>
+      <c r="H36" s="4">
+        <v>3855.06</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
+      <c r="A37" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B37" s="3">
+        <v>46009</v>
+      </c>
+      <c r="C37" s="3">
+        <v>46016</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="F37" s="4">
+        <v>7023</v>
+      </c>
+      <c r="G37" s="4">
+        <v>1474.83</v>
+      </c>
+      <c r="H37" s="4">
+        <v>8497.83</v>
+      </c>
+      <c r="I37" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J37" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
+      <c r="A38" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B38" s="3">
+        <v>46002</v>
+      </c>
+      <c r="C38" s="3">
+        <v>46009</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="F38" s="4">
+        <v>6942</v>
+      </c>
+      <c r="G38" s="4">
+        <v>1457.82</v>
+      </c>
+      <c r="H38" s="4">
+        <v>8399.82</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
+      <c r="A39" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B39" s="3">
+        <v>46002</v>
+      </c>
+      <c r="C39" s="3">
+        <v>46009</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F39" s="4">
+        <v>3216</v>
+      </c>
+      <c r="G39" s="4">
+        <v>675.36</v>
+      </c>
+      <c r="H39" s="4">
+        <v>3891.36</v>
+      </c>
+      <c r="I39" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J39" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10">
+      <c r="A40" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B40" s="3">
+        <v>45995</v>
+      </c>
+      <c r="C40" s="3">
+        <v>46002</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="F40" s="4">
+        <v>9624</v>
+      </c>
+      <c r="G40" s="4">
+        <v>2021.04</v>
+      </c>
+      <c r="H40" s="4">
+        <v>11645.04</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J40" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10">
+      <c r="A41" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B41" s="3">
+        <v>45987</v>
+      </c>
+      <c r="C41" s="3">
+        <v>45994</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F41" s="4">
+        <v>3498</v>
+      </c>
+      <c r="G41" s="4">
+        <v>734.58</v>
+      </c>
+      <c r="H41" s="4">
+        <v>4232.58</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J41" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10">
+      <c r="A42" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B42" s="3">
+        <v>45987</v>
+      </c>
+      <c r="C42" s="3">
+        <v>45994</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="F42" s="4">
+        <v>2766</v>
+      </c>
+      <c r="G42" s="4">
+        <v>580.86</v>
+      </c>
+      <c r="H42" s="4">
+        <v>3346.86</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="A43" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B43" s="3">
+        <v>45987</v>
+      </c>
+      <c r="C43" s="3">
+        <v>45994</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="F43" s="4">
+        <v>3210</v>
+      </c>
+      <c r="G43" s="4">
+        <v>674.1</v>
+      </c>
+      <c r="H43" s="4">
+        <v>3884.1</v>
+      </c>
+      <c r="I43" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J43" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10">
+      <c r="A44" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B44" s="3">
+        <v>45980</v>
+      </c>
+      <c r="C44" s="3">
+        <v>45987</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="F44" s="4">
+        <v>2808</v>
+      </c>
+      <c r="G44" s="4">
+        <v>589.6799999999999</v>
+      </c>
+      <c r="H44" s="4">
+        <v>3397.68</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J44" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10">
+      <c r="A45" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B45" s="3">
+        <v>45980</v>
+      </c>
+      <c r="C45" s="3">
+        <v>45987</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="F45" s="4">
+        <v>2952</v>
+      </c>
+      <c r="G45" s="4">
+        <v>619.92</v>
+      </c>
+      <c r="H45" s="4">
+        <v>3571.92</v>
+      </c>
+      <c r="I45" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J45" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10">
+      <c r="A46" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B46" s="3">
+        <v>45980</v>
+      </c>
+      <c r="C46" s="3">
+        <v>45987</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F46" s="4">
+        <v>3033</v>
+      </c>
+      <c r="G46" s="4">
+        <v>636.9299999999999</v>
+      </c>
+      <c r="H46" s="4">
+        <v>3669.93</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J46" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10">
+      <c r="A47" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B47" s="3">
+        <v>45973</v>
+      </c>
+      <c r="C47" s="3">
+        <v>45980</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="F47" s="4">
+        <v>3129</v>
+      </c>
+      <c r="G47" s="4">
+        <v>657.09</v>
+      </c>
+      <c r="H47" s="4">
+        <v>3786.09</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J47" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10">
+      <c r="A48" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B48" s="3">
+        <v>45973</v>
+      </c>
+      <c r="C48" s="3">
+        <v>45980</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F48" s="4">
+        <v>3873</v>
+      </c>
+      <c r="G48" s="4">
+        <v>813.33</v>
+      </c>
+      <c r="H48" s="4">
+        <v>4686.33</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J48" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10">
+      <c r="A49" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B49" s="3">
+        <v>45973</v>
+      </c>
+      <c r="C49" s="3">
+        <v>45980</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="F49" s="4">
+        <v>3561</v>
+      </c>
+      <c r="G49" s="4">
+        <v>747.8099999999999</v>
+      </c>
+      <c r="H49" s="4">
+        <v>4308.81</v>
+      </c>
+      <c r="I49" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J49" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10">
+      <c r="A50" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B50" s="3">
+        <v>45966</v>
+      </c>
+      <c r="C50" s="3">
+        <v>45973</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="F50" s="4">
+        <v>3762</v>
+      </c>
+      <c r="G50" s="4">
+        <v>790.02</v>
+      </c>
+      <c r="H50" s="4">
+        <v>4552.02</v>
+      </c>
+      <c r="I50" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J50" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10">
+      <c r="A51" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B51" s="3">
+        <v>45966</v>
+      </c>
+      <c r="C51" s="3">
+        <v>45973</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F51" s="4">
+        <v>3501</v>
+      </c>
+      <c r="G51" s="4">
+        <v>735.21</v>
+      </c>
+      <c r="H51" s="4">
+        <v>4236.21</v>
+      </c>
+      <c r="I51" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J51" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10">
+      <c r="A52" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B52" s="3">
+        <v>45966</v>
+      </c>
+      <c r="C52" s="3">
+        <v>45973</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="F52" s="4">
+        <v>2643</v>
+      </c>
+      <c r="G52" s="4">
+        <v>555.03</v>
+      </c>
+      <c r="H52" s="4">
+        <v>3198.03</v>
+      </c>
+      <c r="I52" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J52" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10">
+      <c r="A53" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B53" s="3">
+        <v>45959</v>
+      </c>
+      <c r="C53" s="3">
+        <v>45966</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="F53" s="4">
+        <v>3666</v>
+      </c>
+      <c r="G53" s="4">
+        <v>769.86</v>
+      </c>
+      <c r="H53" s="4">
+        <v>4435.86</v>
+      </c>
+      <c r="I53" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J53" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10">
+      <c r="A54" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B54" s="3">
+        <v>45959</v>
+      </c>
+      <c r="C54" s="3">
+        <v>45966</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="F54" s="4">
+        <v>2784</v>
+      </c>
+      <c r="G54" s="4">
+        <v>584.64</v>
+      </c>
+      <c r="H54" s="4">
+        <v>3368.64</v>
+      </c>
+      <c r="I54" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J54" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10">
+      <c r="A55" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B55" s="3">
+        <v>45959</v>
+      </c>
+      <c r="C55" s="3">
+        <v>45966</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="F55" s="4">
+        <v>3012</v>
+      </c>
+      <c r="G55" s="4">
+        <v>632.52</v>
+      </c>
+      <c r="H55" s="4">
+        <v>3644.52</v>
+      </c>
+      <c r="I55" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J55" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10">
+      <c r="A56" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B56" s="3">
+        <v>45953</v>
+      </c>
+      <c r="C56" s="3">
+        <v>45960</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="F56" s="4">
+        <v>3747</v>
+      </c>
+      <c r="G56" s="4">
+        <v>786.87</v>
+      </c>
+      <c r="H56" s="4">
+        <v>4533.87</v>
+      </c>
+      <c r="I56" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J56" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10">
+      <c r="A57" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B57" s="3">
+        <v>45953</v>
+      </c>
+      <c r="C57" s="3">
+        <v>45960</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="F57" s="4">
+        <v>3243</v>
+      </c>
+      <c r="G57" s="4">
+        <v>681.03</v>
+      </c>
+      <c r="H57" s="4">
+        <v>3924.03</v>
+      </c>
+      <c r="I57" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J57" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10">
+      <c r="A58" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B58" s="3">
+        <v>45953</v>
+      </c>
+      <c r="C58" s="3">
+        <v>45960</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="F58" s="4">
+        <v>2670</v>
+      </c>
+      <c r="G58" s="4">
+        <v>560.7</v>
+      </c>
+      <c r="H58" s="4">
+        <v>3230.7</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J58" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10">
+      <c r="A59" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B59" s="3">
         <v>45947</v>
       </c>
-      <c r="C35" s="3">
+      <c r="C59" s="3">
         <v>45954</v>
       </c>
-      <c r="D35" s="2" t="s">
+      <c r="D59" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E35" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F35" s="4">
-        <v>3001.5</v>
-      </c>
-      <c r="G35" s="4">
-        <v>630.3200000000001</v>
-      </c>
-      <c r="H35" s="4">
-        <v>3631.82</v>
-      </c>
-      <c r="I35" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J35" s="2" t="s">
+      <c r="E59" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="F59" s="4">
+        <v>2931</v>
+      </c>
+      <c r="G59" s="4">
+        <v>615.51</v>
+      </c>
+      <c r="H59" s="4">
+        <v>3546.51</v>
+      </c>
+      <c r="I59" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J59" s="2" t="s">
         <v>14</v>
       </c>
     </row>
